--- a/outputs/48982.xlsx
+++ b/outputs/48982.xlsx
@@ -187,31 +187,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -479,1356 +479,1355 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="4"/>
   </cols>
   <sheetData>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="3" t="n">
         <v>417</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="n">
         <v>418</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="n">
         <v>419</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="n">
         <v>420</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="3" t="n">
         <v>421</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="n">
         <v>422</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="n">
         <v>423</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="n">
         <v>424</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="n">
         <v>425</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="3" t="n">
         <v>426</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="n">
         <v>427</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="n">
         <v>428</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="3" t="n">
         <v>429</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="3" t="n">
         <v>430</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="3" t="n">
         <v>431</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="3" t="n">
         <v>432</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="3" t="n">
         <v>433</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="n">
         <v>434</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="3" t="n">
         <v>435</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="3" t="n">
         <v>436</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="3" t="n">
         <v>437</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="3" t="n">
         <v>438</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="3" t="n">
         <v>439</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="3" t="n">
         <v>440</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="3" t="n">
         <v>441</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="3"/>
     </row>
-    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="3" t="n">
         <v>442</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="3" t="n">
         <v>443</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="3" t="n">
         <v>444</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="3" t="n">
         <v>445</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="3" t="n">
         <v>446</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="3" t="n">
         <v>447</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="3" t="n">
         <v>448</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="3" t="n">
         <v>449</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="3"/>
     </row>
-    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="3" t="n">
         <v>450</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="3" t="n">
         <v>451</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="4" t="n">
         <v>451</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="3" t="n">
         <v>452</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="3" t="n">
         <v>453</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="3"/>
     </row>
-    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="3" t="n">
         <v>454</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="3"/>
     </row>
-    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="3"/>
     </row>
-    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="3"/>
     </row>
-    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="3" t="n">
         <v>455</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="3" t="n">
         <v>456</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="3" t="n">
         <v>457</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="3" t="n">
         <v>458</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="3" t="n">
         <v>459</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="3" t="n">
         <v>460</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="3" t="n">
         <v>461</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="3"/>
     </row>
-    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="3" t="n">
         <v>462</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="3" t="n">
         <v>463</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="3" t="n">
         <v>464</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="3" t="n">
         <v>465</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="3" t="n">
         <v>466</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="3"/>
     </row>
-    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="3"/>
     </row>
-    <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="3"/>
     </row>
-    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="3" t="n">
         <v>467</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="3" t="n">
         <v>468</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="3"/>
     </row>
-    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="3" t="n">
         <v>469</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="3" t="n">
         <v>470</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="3"/>
     </row>
-    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B87" s="3" t="n">
         <v>471</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B88" s="3" t="n">
         <v>472</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B89" s="3"/>
     </row>
-    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B90" s="3" t="n">
         <v>473</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B91" s="3" t="n">
         <v>474</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B92" s="3" t="n">
         <v>475</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B93" s="3" t="n">
         <v>476</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="3" t="n">
         <v>477</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="3"/>
     </row>
-    <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B96" s="3" t="n">
         <v>478</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B97" s="3" t="n">
         <v>479</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="3" t="n">
         <v>480</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="3"/>
     </row>
-    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B100" s="3" t="n">
         <v>481</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="3"/>
     </row>
-    <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="3" t="n">
         <v>482</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B103" s="3"/>
     </row>
-    <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="3" t="n">
         <v>483</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B105" s="3" t="n">
         <v>484</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="3"/>
     </row>
-    <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B107" s="3"/>
     </row>
-    <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B108" s="3" t="n">
         <v>485</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B109" s="3" t="n">
         <v>486</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B110" s="3"/>
     </row>
-    <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B111" s="3" t="n">
         <v>487</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B112" s="3" t="n">
         <v>488</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B113" s="3"/>
     </row>
-    <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B114" s="3" t="n">
         <v>489</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B115" s="3" t="n">
         <v>490</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B116" s="3" t="n">
         <v>491</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B117" s="3"/>
     </row>
-    <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B118" s="3" t="n">
         <v>492</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B119" s="3"/>
     </row>
-    <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B120" s="3"/>
     </row>
-    <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B121" s="3" t="n">
         <v>493</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B122" s="3"/>
     </row>
-    <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B123" s="3"/>
     </row>
-    <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B124" s="3" t="n">
         <v>494</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B125" s="3" t="n">
         <v>495</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B126" s="3"/>
     </row>
-    <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B127" s="3" t="n">
         <v>496</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B128" s="3" t="n">
         <v>497</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B129" s="3" t="n">
         <v>498</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B130" s="3"/>
     </row>
-    <row r="131" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B131" s="3"/>
     </row>
-    <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B132" s="3" t="n">
         <v>499</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B133" s="3" t="n">
         <v>500</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B134" s="3"/>
     </row>
-    <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B135" s="3" t="n">
         <v>501</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B136" s="3"/>
     </row>
-    <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B137" s="5"/>
     </row>
-    <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B138" s="3" t="n">
         <v>502</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B139" s="5"/>
     </row>
-    <row r="140" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B140" s="3" t="n">
         <v>503</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B141" s="3"/>
     </row>
-    <row r="142" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B142" s="3"/>
     </row>
-    <row r="143" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B143" s="3"/>
     </row>
-    <row r="144" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B144" s="3" t="n">
         <v>504</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B145" s="3" t="n">
         <v>505</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B146" s="3" t="n">
         <v>506</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B147" s="3" t="n">
         <v>507</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B148" s="3" t="n">
         <v>508</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B149" s="3"/>
     </row>
-    <row r="150" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B150" s="3" t="n">
         <v>509</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B151" s="3"/>
     </row>
-    <row r="152" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B152" s="3" t="n">
         <v>510</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B153" s="3"/>
     </row>
-    <row r="154" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B154" s="3" t="n">
         <v>511</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B155" s="3" t="n">
         <v>512</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B156" s="3"/>
     </row>
-    <row r="157" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B157" s="3" t="n">
         <v>513</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B158" s="3" t="n">
         <v>514</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B159" s="3" t="n">
         <v>515</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B160" s="3"/>
     </row>
-    <row r="161" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B161" s="3"/>
     </row>
-    <row r="162" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B162" s="3"/>
     </row>
-    <row r="163" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B163" s="3" t="n">
         <v>516</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B164" s="3" t="n">
         <v>517</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B165" s="3" t="n">
         <v>518</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B166" s="3" t="n">
         <v>519</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B167" s="3" t="n">
         <v>520</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B168" s="3" t="n">
         <v>521</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B169" s="3" t="n">
         <v>522</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B170" s="3"/>
     </row>
-    <row r="171" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B171" s="3"/>
     </row>
-    <row r="172" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B172" s="3" t="n">
         <v>523</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B173" s="3" t="n">
         <v>524</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B174" s="3" t="n">
         <v>525</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B175" s="3" t="n">
         <v>526</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B176" s="3" t="n">
         <v>527</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B177" s="3"/>
     </row>
-    <row r="178" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B178" s="3" t="n">
         <v>528</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B179" s="3"/>
     </row>
-    <row r="180" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B180" s="3"/>
     </row>
-    <row r="181" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B181" s="3" t="n">
         <v>529</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B182" s="3" t="n">
         <v>530</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B183" s="3" t="n">
         <v>531</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B184" s="3"/>
     </row>
-    <row r="185" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B185" s="3" t="n">
         <v>532</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B186" s="3" t="n">
         <v>533</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B187" s="3" t="n">
         <v>534</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B188" s="3"/>
     </row>
-    <row r="189" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B189" s="3" t="n">
         <v>535</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B190" s="3" t="n">
         <v>536</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B191" s="3" t="n">
         <v>537</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B192" s="3" t="n">
         <v>538</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B193" s="3" t="n">
         <v>539</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B194" s="3" t="n">
         <v>540</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B195" s="3" t="n">
         <v>541</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B196" s="3"/>
     </row>
-    <row r="197" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B197" s="3" t="n">
         <v>542</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B198" s="3" t="n">
         <v>543</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B199" s="3" t="n">
         <v>544</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B200" s="3" t="n">
         <v>545</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B201" s="3"/>
     </row>
-    <row r="202" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B202" s="3" t="n">
         <v>546</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B203" s="3"/>
     </row>
-    <row r="204" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B204" s="3"/>
     </row>
-    <row r="205" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B205" s="3" t="n">
         <v>547</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B206" s="3" t="n">
         <v>548</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B207" s="3"/>
     </row>
-    <row r="208" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B208" s="3"/>
     </row>
-    <row r="209" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B209" s="3" t="n">
         <v>549</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B210" s="3" t="n">
         <v>550</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B211" s="3" t="n">
         <v>551</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B212" s="3"/>
     </row>
-    <row r="213" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B213" s="3" t="n">
         <v>552</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B214" s="3" t="n">
         <v>553</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B215" s="3" t="n">
         <v>554</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B216" s="3"/>
     </row>
-    <row r="217" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B217" s="3"/>
     </row>
-    <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B218" s="3"/>
     </row>
-    <row r="219" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B219" s="3"/>
     </row>
-    <row r="220" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B220" s="3" t="n">
         <v>555</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B221" s="3" t="n">
         <v>556</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B222" s="3" t="n">
         <v>557</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B223" s="3" t="n">
         <v>558</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B224" s="3" t="n">
         <v>559</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B225" s="3"/>
     </row>
-    <row r="226" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B226" s="3" t="n">
         <v>560</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B227" s="3"/>
     </row>
-    <row r="228" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B228" s="3"/>
     </row>
-    <row r="229" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B229" s="3" t="n">
         <v>561</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B230" s="3"/>
     </row>
-    <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B231" s="3"/>
     </row>
-    <row r="232" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B232" s="3" t="n">
         <v>562</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B233" s="3" t="n">
         <v>563</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B234" s="3"/>
     </row>
-    <row r="235" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B235" s="3" t="n">
         <v>564</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B236" s="3" t="n">
         <v>565</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B237" s="3" t="n">
         <v>566</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B238" s="3" t="n">
         <v>567</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B239" s="3"/>
     </row>
-    <row r="240" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B240" s="3"/>
     </row>
-    <row r="241" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B241" s="3"/>
     </row>
-    <row r="242" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B242" s="3" t="n">
         <v>568</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B243" s="3" t="n">
         <v>569</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B244" s="3"/>
     </row>
-    <row r="245" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B245" s="3"/>
     </row>
-    <row r="246" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B246" s="3" t="n">
         <v>570</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B247" s="3" t="n">
         <v>571</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B248" s="3"/>
     </row>
-    <row r="249" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B249" s="3" t="n">
         <v>572</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B250" s="3" t="n">
         <v>573</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B251" s="3" t="n">
         <v>574</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B252" s="3"/>
     </row>
-    <row r="253" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B253" s="3"/>
     </row>
-    <row r="254" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B254" s="3" t="n">
         <v>575</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B255" s="3" t="n">
         <v>576</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B256" s="3"/>
     </row>
-    <row r="257" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B257" s="3" t="n">
         <v>577</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B258" s="3"/>
     </row>
-    <row r="259" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B259" s="3"/>
     </row>
-    <row r="260" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B260" s="3" t="n">
         <v>578</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B261" s="3"/>
     </row>
-    <row r="262" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B262" s="3" t="n">
         <v>579</v>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B263" s="3" t="n">
         <v>580</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B264" s="3"/>
     </row>
-    <row r="265" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B265" s="3" t="n">
         <v>581</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B266" s="3" t="n">
         <v>582</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B267" s="3"/>
     </row>
-    <row r="268" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B268" s="3"/>
     </row>
-    <row r="269" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B269" s="3" t="n">
         <v>583</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B270" s="3"/>
     </row>
-    <row r="271" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B271" s="3"/>
     </row>
-    <row r="272" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B272" s="3"/>
     </row>
-    <row r="273" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B273" s="3"/>
     </row>
-    <row r="274" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B274" s="3"/>
     </row>
-    <row r="275" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B275" s="3" t="n">
         <v>584</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B276" s="3" t="n">
         <v>585</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B277" s="3" t="n">
         <v>586</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B278" s="3"/>
     </row>
-    <row r="279" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B279" s="3"/>
     </row>
-    <row r="280" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B280" s="3"/>
     </row>
-    <row r="281" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B281" s="3" t="n">
         <v>587</v>
       </c>
     </row>
-    <row r="282" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B282" s="3" t="n">
         <v>588</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B283" s="3" t="n">
         <v>589</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B284" s="3"/>
     </row>
-    <row r="285" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B285" s="3"/>
     </row>
-    <row r="286" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B286" s="3"/>
     </row>
-    <row r="287" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B287" s="3"/>
     </row>
-    <row r="288" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B288" s="3"/>
     </row>
-    <row r="289" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B289" s="3"/>
     </row>
-    <row r="290" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B290" s="3"/>
     </row>
-    <row r="291" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B291" s="3"/>
     </row>
-    <row r="292" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B292" s="3" t="n">
         <v>590</v>
       </c>
     </row>
-    <row r="293" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B293" s="3"/>
     </row>
-    <row r="294" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B294" s="3"/>
     </row>
-    <row r="295" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B295" s="3" t="n">
         <v>591</v>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B296" s="3" t="n">
         <v>592</v>
       </c>
     </row>
-    <row r="297" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B297" s="3"/>
     </row>
-    <row r="298" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B298" s="3" t="n">
         <v>593</v>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B299" s="3"/>
     </row>
-    <row r="300" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B300" s="3"/>
     </row>
-    <row r="301" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B301" s="3" t="n">
         <v>594</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B302" s="3" t="n">
         <v>595</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B303" s="3"/>
     </row>
-    <row r="304" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B304" s="3" t="n">
         <v>596</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B305" s="3" t="n">
         <v>597</v>
       </c>
     </row>
-    <row r="306" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B306" s="3"/>
     </row>
-    <row r="307" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="307" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B307" s="3"/>
     </row>
-    <row r="308" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B308" s="3" t="n">
         <v>598</v>
       </c>
     </row>
-    <row r="309" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B309" s="3"/>
     </row>
-    <row r="310" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B310" s="3"/>
     </row>
-    <row r="311" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B311" s="3" t="n">
         <v>599</v>
       </c>
     </row>
-    <row r="312" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B312" s="3" t="n">
         <v>600</v>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B313" s="3" t="n">
         <v>601</v>
       </c>
     </row>
-    <row r="314" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B314" s="3"/>
     </row>
-    <row r="315" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B315" s="3"/>
     </row>
-    <row r="316" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="6"/>
       <c r="B316" s="3" t="n">
         <v>602</v>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="6"/>
       <c r="B317" s="7" t="n">
         <v>603</v>
       </c>
     </row>
-    <row r="318" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B318" s="3"/>
     </row>
-    <row r="319" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="319" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="6"/>
       <c r="B319" s="3" t="n">
         <v>604</v>
       </c>
     </row>
-    <row r="320" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="6"/>
       <c r="B320" s="3" t="n">
         <v>605</v>
       </c>
     </row>
-    <row r="321" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="6"/>
     </row>
-    <row r="322" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="322" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B322" s="3"/>
     </row>
-    <row r="323" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B323" s="8" t="n">
-        <f aca="false">IF(A323="E","",MAX(B$7:B322)+1)</f>
         <v>606</v>
       </c>
     </row>
-    <row r="326" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="326" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B326" s="9"/>
     </row>
   </sheetData>
